--- a/docs/PEPTIDEX_Estudio_Mercado.xlsx
+++ b/docs/PEPTIDEX_Estudio_Mercado.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FUENTES" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MÉXICO'!$A$5:$E$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'USA'!$A$5:$E$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MÉXICO'!$A$5:$G$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'USA'!$A$5:$G$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,9 +75,20 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="001E5EFF"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="002F7A3D"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005F6875"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -127,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,9 +163,18 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -173,16 +193,13 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -550,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B22"/>
+  <dimension ref="B2:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -581,7 +598,7 @@
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>MÉXICO   ·  las 118 presentaciones con su precio al consumidor en pesos, y su equivalente en dólares al lado.</t>
+          <t>MÉXICO   ·  las 118 presentaciones con su precio al consumidor en pesos, su equivalente en dólares, y en qué se basa ese precio.</t>
         </is>
       </c>
     </row>
@@ -595,75 +612,103 @@
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Y TRES QUE SOSTIENEN EL NÚMERO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>CADA PRECIO DICE DE DÓNDE SALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN  ·  de dónde sale el precio, en cinco líneas, y qué contesta y qué no.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
+          <t>La columna EN QUÉ SE BASA ESTE PRECIO trae, en la misma fila, la cifra de mercado de la que se calculó y quién la publica.  No hay que ir a buscarla a otra hoja para saber si creérsela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BANDAS   ·  el precio de mercado por unidad de cada compuesto, con su fuente.  Es el único sitio con números escritos a mano: las 236 filas de las dos listas son fórmulas contra él.  Cambia ahí el tipo de cambio y se actualiza el libro entero.</t>
+          <t>Y la columna CONF. dice cuánto vale ese respaldo.  V: hay una cifra publicada para ESE compuesto — once de las cincuenta y seis.  D: no la hay, y se usa la banda de su clase, que sí está comprobada — las otras cuarenta y cinco, con la clase escrita al lado.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>FUENTES  ·  cada enlace consultado y qué dato dio.</t>
+          <t>El enlace concreto de cada compuesto está en BANDAS, y todos juntos en FUENTES.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>CÓMO SE LLEGÓ AL PRECIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
+          <t>Y TRES QUE SOSTIENEN EL NÚMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>El mercado no cotiza viales, cotiza materia: el vial de 20 mg vale cuatro veces el de 5 mg del mismo compuesto.  Así que se busca el precio por unidad de cada compuesto —por mg casi siempre— y se multiplica por la cantidad de la presentación.</t>
+          <t>RESUMEN  ·  de dónde sale el precio, en cinco líneas, y qué contesta y qué no.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>De cada compuesto se localizó el más barato y el más caro del mercado.  El precio de las listas es el punto medio: ni el suelo, que es guerra de precio, ni el techo, que sólo lo sostiene una marca ya conocida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>DOS COSAS QUE CONVIENE SABER</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>De las 56 moléculas, 11 tienen una cifra publicada para ese compuesto exacto y 45 usan la banda de su clase, que sí está comprobada.  En BANDAS van marcadas V y D.  Antes de fijar precio en los diez que más vendas, abre esas fuentes y confirma el número del día.</t>
+          <t>BANDAS   ·  el precio de mercado por unidad de cada compuesto, con su fuente.  Es el único sitio con números escritos a mano: las 236 filas de las dos listas son fórmulas contra él.  Cambia ahí el tipo de cambio y se actualiza el libro entero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>FUENTES  ·  cada enlace consultado y qué dato dio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>CÓMO SE LLEGÓ AL PRECIO</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>El mercado no cotiza viales, cotiza materia: el vial de 20 mg vale cuatro veces el de 5 mg del mismo compuesto.  Así que se busca el precio por unidad de cada compuesto —por mg casi siempre— y se multiplica por la cantidad de la presentación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>De cada compuesto se localizó el más barato y el más caro del mercado.  El precio de las listas es el punto medio: ni el suelo, que es guerra de precio, ni el techo, que sólo lo sostiene una marca ya conocida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>DOS COSAS QUE CONVIENE SABER</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>De las 56 moléculas, 11 tienen una cifra publicada para ese compuesto exacto y 45 usan la banda de su clase, que sí está comprobada.  En BANDAS van marcadas V y D.  Antes de fijar precio en los diez que más vendas, abre esas fuentes y confirma el número del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>Las columnas de precio son fórmulas: se calculan al abrir el libro en Excel, Google Sheets o Numbers.  En la vista previa del teléfono pueden salir vacías — no es un error del archivo.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="2" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Research Use Only — no para uso humano ni veterinario.</t>
         </is>
@@ -680,14 +725,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E123"/>
+  <dimension ref="A2:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="86" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -730,8 +777,18 @@
           <t>EQUIVALE A (USD)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>EN QUÉ SE BASA ESTE PRECIO</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>CONF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -755,8 +812,16 @@
         <f>D6/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="7">
+      <c r="F6" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B6,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B6,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -780,8 +845,16 @@
         <f>D7/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
+      <c r="F7" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B7,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B7,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -805,8 +878,16 @@
         <f>D8/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="9">
+      <c r="F8" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B8,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B8,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -830,8 +911,16 @@
         <f>D9/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="10">
+      <c r="F9" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B9,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B9,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -855,8 +944,16 @@
         <f>D10/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="11">
+      <c r="F10" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B10,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G10" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B10,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -880,8 +977,16 @@
         <f>D11/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="12">
+      <c r="F11" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B11,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B11,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -905,8 +1010,16 @@
         <f>D12/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="13">
+      <c r="F12" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B12,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B12,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -930,8 +1043,16 @@
         <f>D13/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="14">
+      <c r="F13" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B13,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B13,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -955,8 +1076,16 @@
         <f>D14/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="15">
+      <c r="F14" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B14,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G14" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B14,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -980,8 +1109,16 @@
         <f>D15/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="16">
+      <c r="F15" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B15,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G15" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B15,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -1005,8 +1142,16 @@
         <f>D16/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="17">
+      <c r="F16" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B16,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B16,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -1030,8 +1175,16 @@
         <f>D17/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="18">
+      <c r="F17" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B17,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G17" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B17,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -1055,8 +1208,16 @@
         <f>D18/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="19">
+      <c r="F18" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B18,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B18,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -1080,8 +1241,16 @@
         <f>D19/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="20">
+      <c r="F19" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B19,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G19" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B19,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -1105,8 +1274,16 @@
         <f>D20/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="21">
+      <c r="F20" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B20,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B20,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -1130,8 +1307,16 @@
         <f>D21/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="22">
+      <c r="F21" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B21,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G21" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B21,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1155,8 +1340,16 @@
         <f>D22/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="23">
+      <c r="F22" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B22,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G22" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B22,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1180,8 +1373,16 @@
         <f>D23/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="24">
+      <c r="F23" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B23,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G23" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B23,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1205,8 +1406,16 @@
         <f>D24/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="25">
+      <c r="F24" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B24,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G24" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B24,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1230,8 +1439,16 @@
         <f>D25/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="26">
+      <c r="F25" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B25,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G25" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B25,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1255,8 +1472,16 @@
         <f>D26/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="27">
+      <c r="F26" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B26,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G26" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B26,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1280,8 +1505,16 @@
         <f>D27/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="28">
+      <c r="F27" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B27,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G27" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B27,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1305,8 +1538,16 @@
         <f>D28/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="29">
+      <c r="F28" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B28,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G28" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B28,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1330,8 +1571,16 @@
         <f>D29/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="30">
+      <c r="F29" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B29,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G29" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B29,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1355,8 +1604,16 @@
         <f>D30/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="31">
+      <c r="F30" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B30,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G30" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B30,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1380,8 +1637,16 @@
         <f>D31/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="32">
+      <c r="F31" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B31,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B31,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1405,8 +1670,16 @@
         <f>D32/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="33">
+      <c r="F32" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B32,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G32" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B32,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1430,8 +1703,16 @@
         <f>D33/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="34">
+      <c r="F33" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B33,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G33" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B33,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1455,8 +1736,16 @@
         <f>D34/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="35">
+      <c r="F34" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B34,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G34" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B34,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1480,8 +1769,16 @@
         <f>D35/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="36">
+      <c r="F35" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B35,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G35" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B35,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1505,8 +1802,16 @@
         <f>D36/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="37">
+      <c r="F36" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B36,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G36" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B36,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1530,8 +1835,16 @@
         <f>D37/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="38">
+      <c r="F37" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B37,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G37" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B37,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1555,8 +1868,16 @@
         <f>D38/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="39">
+      <c r="F38" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B38,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G38" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B38,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1580,8 +1901,16 @@
         <f>D39/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="40">
+      <c r="F39" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B39,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G39" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B39,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1605,8 +1934,16 @@
         <f>D40/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="41">
+      <c r="F40" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B40,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G40" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B40,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1630,8 +1967,16 @@
         <f>D41/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="42">
+      <c r="F41" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B41,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G41" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B41,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1655,8 +2000,16 @@
         <f>D42/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="43">
+      <c r="F42" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B42,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G42" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B42,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1680,8 +2033,16 @@
         <f>D43/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="44">
+      <c r="F43" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B43,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G43" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B43,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1705,8 +2066,16 @@
         <f>D44/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="45">
+      <c r="F44" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B44,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G44" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B44,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1730,8 +2099,16 @@
         <f>D45/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="46">
+      <c r="F45" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B45,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G45" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B45,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1755,8 +2132,16 @@
         <f>D46/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="47">
+      <c r="F46" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B46,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G46" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B46,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1780,8 +2165,16 @@
         <f>D47/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="48">
+      <c r="F47" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B47,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G47" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B47,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1805,8 +2198,16 @@
         <f>D48/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="49">
+      <c r="F48" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B48,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G48" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B48,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1830,8 +2231,16 @@
         <f>D49/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="50">
+      <c r="F49" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B49,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G49" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B49,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1855,8 +2264,16 @@
         <f>D50/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="51">
+      <c r="F50" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B50,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G50" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B50,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1880,8 +2297,16 @@
         <f>D51/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="52">
+      <c r="F51" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B51,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G51" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B51,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1905,8 +2330,16 @@
         <f>D52/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="53">
+      <c r="F52" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B52,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G52" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B52,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1930,8 +2363,16 @@
         <f>D53/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="54">
+      <c r="F53" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B53,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G53" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B53,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1955,8 +2396,16 @@
         <f>D54/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="55">
+      <c r="F54" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B54,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G54" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B54,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -1980,8 +2429,16 @@
         <f>D55/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="56">
+      <c r="F55" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B55,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G55" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B55,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2005,8 +2462,16 @@
         <f>D56/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="57">
+      <c r="F56" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B56,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G56" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B56,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2030,8 +2495,16 @@
         <f>D57/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="58">
+      <c r="F57" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B57,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G57" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B57,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2055,8 +2528,16 @@
         <f>D58/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="59">
+      <c r="F58" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B58,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G58" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B58,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2080,8 +2561,16 @@
         <f>D59/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="60">
+      <c r="F59" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B59,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G59" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B59,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2105,8 +2594,16 @@
         <f>D60/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="61">
+      <c r="F60" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B60,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G60" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B60,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2130,8 +2627,16 @@
         <f>D61/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="62">
+      <c r="F61" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B61,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G61" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B61,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2155,8 +2660,16 @@
         <f>D62/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="63">
+      <c r="F62" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B62,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G62" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B62,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2180,8 +2693,16 @@
         <f>D63/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="64">
+      <c r="F63" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B63,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G63" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B63,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2205,8 +2726,16 @@
         <f>D64/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="65">
+      <c r="F64" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B64,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G64" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B64,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2230,8 +2759,16 @@
         <f>D65/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="66">
+      <c r="F65" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B65,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B65,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2255,8 +2792,16 @@
         <f>D66/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="67">
+      <c r="F66" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B66,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B66,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2280,8 +2825,16 @@
         <f>D67/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="68">
+      <c r="F67" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B67,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G67" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B67,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2305,8 +2858,16 @@
         <f>D68/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="69">
+      <c r="F68" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B68,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G68" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B68,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2330,8 +2891,16 @@
         <f>D69/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="70">
+      <c r="F69" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B69,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G69" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B69,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2355,8 +2924,16 @@
         <f>D70/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="71">
+      <c r="F70" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B70,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G70" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B70,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2380,8 +2957,16 @@
         <f>D71/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="72">
+      <c r="F71" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B71,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G71" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B71,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2405,8 +2990,16 @@
         <f>D72/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="73">
+      <c r="F72" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B72,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G72" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B72,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2430,8 +3023,16 @@
         <f>D73/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="74">
+      <c r="F73" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B73,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G73" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B73,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2455,8 +3056,16 @@
         <f>D74/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="75">
+      <c r="F74" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B74,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G74" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B74,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2480,8 +3089,16 @@
         <f>D75/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="76">
+      <c r="F75" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B75,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G75" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B75,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2505,8 +3122,16 @@
         <f>D76/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="77">
+      <c r="F76" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B76,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G76" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B76,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2530,8 +3155,16 @@
         <f>D77/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="78">
+      <c r="F77" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B77,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G77" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B77,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2555,8 +3188,16 @@
         <f>D78/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="79">
+      <c r="F78" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B78,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G78" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B78,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2580,8 +3221,16 @@
         <f>D79/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="80">
+      <c r="F79" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B79,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G79" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B79,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2605,8 +3254,16 @@
         <f>D80/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="81">
+      <c r="F80" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B80,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G80" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B80,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2630,8 +3287,16 @@
         <f>D81/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="82">
+      <c r="F81" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B81,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G81" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B81,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2655,8 +3320,16 @@
         <f>D82/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="83">
+      <c r="F82" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B82,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G82" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B82,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2680,8 +3353,16 @@
         <f>D83/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="84">
+      <c r="F83" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B83,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G83" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B83,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2705,8 +3386,16 @@
         <f>D84/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="85">
+      <c r="F84" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B84,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G84" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B84,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2730,8 +3419,16 @@
         <f>D85/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="86">
+      <c r="F85" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B85,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G85" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B85,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2755,8 +3452,16 @@
         <f>D86/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="87">
+      <c r="F86" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B86,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G86" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B86,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2780,8 +3485,16 @@
         <f>D87/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="88">
+      <c r="F87" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B87,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G87" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B87,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2805,8 +3518,16 @@
         <f>D88/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="89">
+      <c r="F88" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B88,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G88" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B88,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2830,8 +3551,16 @@
         <f>D89/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="90">
+      <c r="F89" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B89,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G89" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B89,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2855,8 +3584,16 @@
         <f>D90/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="91">
+      <c r="F90" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B90,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G90" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B90,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2880,8 +3617,16 @@
         <f>D91/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="92">
+      <c r="F91" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B91,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G91" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B91,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2905,8 +3650,16 @@
         <f>D92/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="93">
+      <c r="F92" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B92,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G92" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B92,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2930,8 +3683,16 @@
         <f>D93/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="94">
+      <c r="F93" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B93,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G93" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B93,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2955,8 +3716,16 @@
         <f>D94/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="95">
+      <c r="F94" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B94,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G94" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B94,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="26" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -2980,8 +3749,16 @@
         <f>D95/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="96">
+      <c r="F95" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B95,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G95" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B95,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -3005,8 +3782,16 @@
         <f>D96/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="97">
+      <c r="F96" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B96,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G96" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B96,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="26" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -3030,8 +3815,16 @@
         <f>D97/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="98">
+      <c r="F97" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B97,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G97" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B97,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="26" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -3055,8 +3848,16 @@
         <f>D98/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="99">
+      <c r="F98" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B98,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G98" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B98,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="26" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -3080,8 +3881,16 @@
         <f>D99/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="100">
+      <c r="F99" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B99,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G99" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B99,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="26" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3105,8 +3914,16 @@
         <f>D100/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="101">
+      <c r="F100" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B100,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G100" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B100,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="26" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3130,8 +3947,16 @@
         <f>D101/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="102">
+      <c r="F101" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B101,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G101" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B101,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="26" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3155,8 +3980,16 @@
         <f>D102/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="103">
+      <c r="F102" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B102,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G102" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B102,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="26" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3180,8 +4013,16 @@
         <f>D103/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="104">
+      <c r="F103" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B103,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G103" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B103,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="26" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3205,8 +4046,16 @@
         <f>D104/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="105">
+      <c r="F104" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B104,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G104" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B104,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="26" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3230,8 +4079,16 @@
         <f>D105/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="106">
+      <c r="F105" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B105,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G105" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B105,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="26" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3255,8 +4112,16 @@
         <f>D106/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="107">
+      <c r="F106" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B106,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G106" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B106,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="26" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3280,8 +4145,16 @@
         <f>D107/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="108">
+      <c r="F107" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B107,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G107" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B107,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="26" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3305,8 +4178,16 @@
         <f>D108/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="109">
+      <c r="F108" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B108,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G108" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B108,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="26" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3330,8 +4211,16 @@
         <f>D109/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="110">
+      <c r="F109" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B109,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G109" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B109,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="26" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3355,8 +4244,16 @@
         <f>D110/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="111">
+      <c r="F110" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B110,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G110" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B110,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="26" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3380,8 +4277,16 @@
         <f>D111/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="112">
+      <c r="F111" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B111,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G111" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B111,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="26" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3405,8 +4310,16 @@
         <f>D112/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="113">
+      <c r="F112" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B112,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G112" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B112,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="26" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3430,8 +4343,16 @@
         <f>D113/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="114">
+      <c r="F113" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B113,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G113" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B113,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3455,8 +4376,16 @@
         <f>D114/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="115">
+      <c r="F114" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B114,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G114" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B114,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="26" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3480,8 +4409,16 @@
         <f>D115/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="116">
+      <c r="F115" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B115,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G115" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B115,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="26" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3505,8 +4442,16 @@
         <f>D116/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="117">
+      <c r="F116" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B116,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G116" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B116,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="26" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3530,8 +4475,16 @@
         <f>D117/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="118">
+      <c r="F117" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B117,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G117" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B117,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="26" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3555,8 +4508,16 @@
         <f>D118/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="119">
+      <c r="F118" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B118,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G118" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B118,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="26" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3580,8 +4541,16 @@
         <f>D119/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="120">
+      <c r="F119" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B119,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G119" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B119,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="26" customHeight="1">
       <c r="A120" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3605,8 +4574,16 @@
         <f>D120/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="121">
+      <c r="F120" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B120,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G120" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B120,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="26" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3630,8 +4607,16 @@
         <f>D121/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="122">
+      <c r="F121" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B121,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G121" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B121,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="26" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3655,8 +4640,16 @@
         <f>D122/BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="123">
+      <c r="F122" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B122,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G122" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B122,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -3680,9 +4673,17 @@
         <f>D123/BANDAS!$E$5</f>
         <v/>
       </c>
+      <c r="F123" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B123,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G123" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B123,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:E123"/>
+  <autoFilter ref="A5:G123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3693,14 +4694,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E123"/>
+  <dimension ref="A2:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="86" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -3743,8 +4746,18 @@
           <t>EQUIVALE A (MXN)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>EN QUÉ SE BASA ESTE PRECIO</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>CONF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3760,16 +4773,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$9,BANDAS!$F$9)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="16">
         <f>D6*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="7">
+      <c r="F6" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B6,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B6,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3785,16 +4806,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$9,BANDAS!$F$9)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <f>D7*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
+      <c r="F7" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B7,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B7,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3810,16 +4839,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$10,BANDAS!$F$10)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="16">
         <f>D8*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="9">
+      <c r="F8" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B8,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B8,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3835,16 +4872,24 @@
           <t>100 mg</t>
         </is>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$10,BANDAS!$F$10)*100/1,0)*1</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <f>D9*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="10">
+      <c r="F9" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B9,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B9,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3860,16 +4905,24 @@
           <t>70 mg</t>
         </is>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$11,BANDAS!$F$11)*70/1,0)*1</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="16">
         <f>D10*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="11">
+      <c r="F10" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B10,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G10" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B10,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3885,16 +4938,24 @@
           <t>600 mg</t>
         </is>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$12,BANDAS!$F$12)*600/1,0)*1</f>
         <v/>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="16">
         <f>D11*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="12">
+      <c r="F11" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B11,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B11,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3910,16 +4971,24 @@
           <t>1500 mg</t>
         </is>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$12,BANDAS!$F$12)*1500/1,0)*1</f>
         <v/>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="16">
         <f>D12*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="13">
+      <c r="F12" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B12,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B12,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3935,16 +5004,24 @@
           <t>80 mg</t>
         </is>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$13,BANDAS!$F$13)*80/1,0)*1</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="16">
         <f>D13*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="14">
+      <c r="F13" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B13,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B13,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3960,16 +5037,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$14,BANDAS!$F$14)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="16">
         <f>D14*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="15">
+      <c r="F14" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B14,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G14" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B14,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -3985,16 +5070,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$14,BANDAS!$F$14)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="16">
         <f>D15*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="16">
+      <c r="F15" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B15,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G15" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B15,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -4010,16 +5103,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$15,BANDAS!$F$15)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="16">
         <f>D16*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="17">
+      <c r="F16" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B16,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B16,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -4035,16 +5136,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$16,BANDAS!$F$16)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="16">
         <f>D17*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="18">
+      <c r="F17" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B17,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G17" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B17,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -4060,16 +5169,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$17,BANDAS!$F$17)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="16">
         <f>D18*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="19">
+      <c r="F18" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B18,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B18,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -4085,16 +5202,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$18,BANDAS!$F$18)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="16">
         <f>D19*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="20">
+      <c r="F19" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B19,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G19" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B19,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -4110,16 +5235,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$19,BANDAS!$F$19)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="16">
         <f>D20*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="21">
+      <c r="F20" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B20,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B20,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>BEAUTY</t>
@@ -4135,16 +5268,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$20,BANDAS!$F$20)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="16">
         <f>D21*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="22">
+      <c r="F21" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B21,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G21" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B21,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4160,16 +5301,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$21,BANDAS!$F$21)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="16">
         <f>D22*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="23">
+      <c r="F22" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B22,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G22" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B22,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4185,16 +5334,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$21,BANDAS!$F$21)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="16">
         <f>D23*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="24">
+      <c r="F23" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B23,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G23" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B23,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4210,16 +5367,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$21,BANDAS!$F$21)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="16">
         <f>D24*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="25">
+      <c r="F24" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B24,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G24" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B24,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4235,16 +5400,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$22,BANDAS!$F$22)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="16">
         <f>D25*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="26">
+      <c r="F25" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B25,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G25" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B25,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4260,16 +5433,24 @@
           <t>100 mg</t>
         </is>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$22,BANDAS!$F$22)*100/1,0)*1</f>
         <v/>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="16">
         <f>D26*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="27">
+      <c r="F26" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B26,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G26" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B26,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4285,16 +5466,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$23,BANDAS!$F$23)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="16">
         <f>D27*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="28">
+      <c r="F27" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B27,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G27" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B27,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4310,16 +5499,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$23,BANDAS!$F$23)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="16">
         <f>D28*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="29">
+      <c r="F28" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B28,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G28" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B28,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4335,16 +5532,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$24,BANDAS!$F$24)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="16">
         <f>D29*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="30">
+      <c r="F29" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B29,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G29" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B29,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4360,16 +5565,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$25,BANDAS!$F$25)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="16">
         <f>D30*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="31">
+      <c r="F30" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B30,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G30" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B30,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4385,16 +5598,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$25,BANDAS!$F$25)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="16">
         <f>D31*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="32">
+      <c r="F31" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B31,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B31,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4410,16 +5631,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$26,BANDAS!$F$26)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="16">
         <f>D32*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="33">
+      <c r="F32" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B32,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G32" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B32,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4435,16 +5664,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$27,BANDAS!$F$27)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="16">
         <f>D33*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="34">
+      <c r="F33" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B33,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G33" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B33,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4460,16 +5697,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$27,BANDAS!$F$27)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="16">
         <f>D34*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="35">
+      <c r="F34" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B34,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G34" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B34,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4485,16 +5730,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$27,BANDAS!$F$27)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="16">
         <f>D35*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="36">
+      <c r="F35" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B35,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G35" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B35,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4510,16 +5763,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$28,BANDAS!$F$28)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="16">
         <f>D36*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="37">
+      <c r="F36" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B36,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G36" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B36,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4535,16 +5796,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$28,BANDAS!$F$28)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="16">
         <f>D37*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="38">
+      <c r="F37" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B37,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G37" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B37,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4560,16 +5829,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$29,BANDAS!$F$29)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="16">
         <f>D38*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="39">
+      <c r="F38" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B38,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G38" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B38,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4585,16 +5862,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$29,BANDAS!$F$29)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="16">
         <f>D39*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="40">
+      <c r="F39" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B39,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G39" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B39,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4610,16 +5895,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$30,BANDAS!$F$30)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="16">
         <f>D40*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="41">
+      <c r="F40" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B40,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G40" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B40,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4635,16 +5928,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$30,BANDAS!$F$30)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="16">
         <f>D41*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="42">
+      <c r="F41" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B41,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G41" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B41,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4660,16 +5961,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$31,BANDAS!$F$31)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="16">
         <f>D42*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="43">
+      <c r="F42" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B42,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G42" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B42,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4685,16 +5994,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$32,BANDAS!$F$32)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="16">
         <f>D43*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="44">
+      <c r="F43" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B43,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G43" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B43,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4710,16 +6027,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$32,BANDAS!$F$32)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="16">
         <f>D44*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="45">
+      <c r="F44" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B44,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G44" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B44,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4735,16 +6060,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$33,BANDAS!$F$33)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="16">
         <f>D45*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="46">
+      <c r="F45" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B45,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G45" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B45,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4760,16 +6093,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$33,BANDAS!$F$33)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="16">
         <f>D46*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="47">
+      <c r="F46" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B46,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G46" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B46,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4785,16 +6126,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$34,BANDAS!$F$34)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="16">
         <f>D47*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="48">
+      <c r="F47" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B47,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G47" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B47,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4810,16 +6159,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$34,BANDAS!$F$34)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="16">
         <f>D48*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="49">
+      <c r="F48" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B48,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G48" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B48,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4835,16 +6192,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$35,BANDAS!$F$35)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="16">
         <f>D49*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="50">
+      <c r="F49" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B49,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G49" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B49,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4860,16 +6225,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$35,BANDAS!$F$35)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="16">
         <f>D50*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="51">
+      <c r="F50" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B50,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G50" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B50,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4885,16 +6258,24 @@
           <t>10 iu</t>
         </is>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$36,BANDAS!$F$36)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E51" s="13">
+      <c r="E51" s="16">
         <f>D51*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="52">
+      <c r="F51" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B51,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G51" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B51,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4910,16 +6291,24 @@
           <t>12 iu</t>
         </is>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$36,BANDAS!$F$36)*12/1,0)*1</f>
         <v/>
       </c>
-      <c r="E52" s="13">
+      <c r="E52" s="16">
         <f>D52*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="53">
+      <c r="F52" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B52,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G52" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B52,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4935,16 +6324,24 @@
           <t>15 iu</t>
         </is>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$36,BANDAS!$F$36)*15/1,0)*1</f>
         <v/>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="16">
         <f>D53*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="54">
+      <c r="F53" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B53,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G53" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B53,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4960,16 +6357,24 @@
           <t>24 iu</t>
         </is>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$36,BANDAS!$F$36)*24/1,0)*1</f>
         <v/>
       </c>
-      <c r="E54" s="13">
+      <c r="E54" s="16">
         <f>D54*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="55">
+      <c r="F54" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B54,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G54" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B54,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -4985,16 +6390,24 @@
           <t>36 iu</t>
         </is>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$36,BANDAS!$F$36)*36/1,0)*1</f>
         <v/>
       </c>
-      <c r="E55" s="13">
+      <c r="E55" s="16">
         <f>D55*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="56">
+      <c r="F55" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B55,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G55" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B55,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5010,16 +6423,24 @@
           <t>2 mg</t>
         </is>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$37,BANDAS!$F$37)*2/1,0)*1</f>
         <v/>
       </c>
-      <c r="E56" s="13">
+      <c r="E56" s="16">
         <f>D56*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="57">
+      <c r="F56" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B56,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G56" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B56,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5035,16 +6456,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$37,BANDAS!$F$37)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="16">
         <f>D57*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="58">
+      <c r="F57" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B57,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G57" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B57,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5060,16 +6489,24 @@
           <t>0.1 mg</t>
         </is>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$38,BANDAS!$F$38)*0.1/1,0)*1</f>
         <v/>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="16">
         <f>D58*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="59">
+      <c r="F58" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B58,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G58" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B58,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5085,16 +6522,24 @@
           <t>1 mg</t>
         </is>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$38,BANDAS!$F$38)*1/1,0)*1</f>
         <v/>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="16">
         <f>D59*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="60">
+      <c r="F59" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B59,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G59" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B59,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5110,16 +6555,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$39,BANDAS!$F$39)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E60" s="13">
+      <c r="E60" s="16">
         <f>D60*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="61">
+      <c r="F60" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B60,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G60" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B60,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5135,16 +6588,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$39,BANDAS!$F$39)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E61" s="13">
+      <c r="E61" s="16">
         <f>D61*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="62">
+      <c r="F61" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B61,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G61" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B61,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5160,16 +6621,24 @@
           <t>600 mg</t>
         </is>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$40,BANDAS!$F$40)*600/1,0)*1</f>
         <v/>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="16">
         <f>D62*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="63">
+      <c r="F62" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B62,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G62" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B62,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5185,16 +6654,24 @@
           <t>1200 mg</t>
         </is>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$40,BANDAS!$F$40)*1200/1,0)*1</f>
         <v/>
       </c>
-      <c r="E63" s="13">
+      <c r="E63" s="16">
         <f>D63*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="64">
+      <c r="F63" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B63,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G63" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B63,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5210,16 +6687,24 @@
           <t>10 ml</t>
         </is>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$41,BANDAS!$F$41)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="16">
         <f>D64*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="65">
+      <c r="F64" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B64,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G64" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B64,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5235,16 +6720,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$42,BANDAS!$F$42)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="16">
         <f>D65*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="66">
+      <c r="F65" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B65,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B65,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5260,16 +6753,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$42,BANDAS!$F$42)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="16">
         <f>D66*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="67">
+      <c r="F66" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B66,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B66,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5285,16 +6786,24 @@
           <t>40 mg</t>
         </is>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$42,BANDAS!$F$42)*40/1,0)*1</f>
         <v/>
       </c>
-      <c r="E67" s="13">
+      <c r="E67" s="16">
         <f>D67*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="68">
+      <c r="F67" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B67,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G67" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B67,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5310,16 +6819,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$43,BANDAS!$F$43)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="16">
         <f>D68*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="69">
+      <c r="F68" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B68,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G68" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B68,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5335,16 +6852,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$43,BANDAS!$F$43)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="16">
         <f>D69*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="70">
+      <c r="F69" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B69,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G69" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B69,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5360,16 +6885,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="16">
         <f>D70*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="71">
+      <c r="F70" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B70,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G70" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B70,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5385,16 +6918,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="16">
         <f>D71*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="72">
+      <c r="F71" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B71,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G71" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B71,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5410,16 +6951,24 @@
           <t>15 mg</t>
         </is>
       </c>
-      <c r="D72" s="12">
+      <c r="D72" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*15/1,0)*1</f>
         <v/>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="16">
         <f>D72*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="73">
+      <c r="F72" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B72,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G72" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B72,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5435,16 +6984,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="16">
         <f>D73*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="74">
+      <c r="F73" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B73,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G73" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B73,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5460,16 +7017,24 @@
           <t>30 mg</t>
         </is>
       </c>
-      <c r="D74" s="12">
+      <c r="D74" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*30/1,0)*1</f>
         <v/>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="16">
         <f>D74*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="75">
+      <c r="F74" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B74,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G74" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B74,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5485,16 +7050,24 @@
           <t>40 mg</t>
         </is>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*40/1,0)*1</f>
         <v/>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="16">
         <f>D75*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="76">
+      <c r="F75" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B75,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G75" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B75,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5510,16 +7083,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="16">
         <f>D76*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="77">
+      <c r="F76" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B76,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G76" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B76,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5535,16 +7116,24 @@
           <t>60 mg</t>
         </is>
       </c>
-      <c r="D77" s="12">
+      <c r="D77" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$44,BANDAS!$F$44)*60/1,0)*1</f>
         <v/>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="16">
         <f>D77*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="78">
+      <c r="F77" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B77,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G77" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B77,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5560,16 +7149,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D78" s="12">
+      <c r="D78" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$45,BANDAS!$F$45)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="16">
         <f>D78*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="79">
+      <c r="F78" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B78,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G78" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B78,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5585,16 +7182,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D79" s="12">
+      <c r="D79" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$45,BANDAS!$F$45)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="16">
         <f>D79*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="80">
+      <c r="F79" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B79,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G79" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B79,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5610,16 +7215,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D80" s="12">
+      <c r="D80" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$46,BANDAS!$F$46)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E80" s="13">
+      <c r="E80" s="16">
         <f>D80*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="81">
+      <c r="F80" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B80,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G80" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B80,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5635,16 +7248,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$46,BANDAS!$F$46)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E81" s="13">
+      <c r="E81" s="16">
         <f>D81*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="82">
+      <c r="F81" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B81,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G81" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B81,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5660,16 +7281,24 @@
           <t>15 mg</t>
         </is>
       </c>
-      <c r="D82" s="12">
+      <c r="D82" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$46,BANDAS!$F$46)*15/1,0)*1</f>
         <v/>
       </c>
-      <c r="E82" s="13">
+      <c r="E82" s="16">
         <f>D82*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="83">
+      <c r="F82" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B82,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G82" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B82,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5685,16 +7314,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D83" s="12">
+      <c r="D83" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$46,BANDAS!$F$46)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E83" s="13">
+      <c r="E83" s="16">
         <f>D83*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="84">
+      <c r="F83" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B83,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G83" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B83,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5710,16 +7347,24 @@
           <t>30 mg</t>
         </is>
       </c>
-      <c r="D84" s="12">
+      <c r="D84" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$46,BANDAS!$F$46)*30/1,0)*1</f>
         <v/>
       </c>
-      <c r="E84" s="13">
+      <c r="E84" s="16">
         <f>D84*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="85">
+      <c r="F84" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B84,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G84" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B84,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5735,16 +7380,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D85" s="12">
+      <c r="D85" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$47,BANDAS!$F$47)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E85" s="13">
+      <c r="E85" s="16">
         <f>D85*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="86">
+      <c r="F85" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B85,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G85" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B85,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5760,16 +7413,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D86" s="12">
+      <c r="D86" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$47,BANDAS!$F$47)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E86" s="13">
+      <c r="E86" s="16">
         <f>D86*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="87">
+      <c r="F86" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B86,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G86" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B86,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5785,16 +7446,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D87" s="12">
+      <c r="D87" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$48,BANDAS!$F$48)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E87" s="13">
+      <c r="E87" s="16">
         <f>D87*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="88">
+      <c r="F87" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B87,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G87" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B87,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5810,16 +7479,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D88" s="12">
+      <c r="D88" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$48,BANDAS!$F$48)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E88" s="13">
+      <c r="E88" s="16">
         <f>D88*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="89">
+      <c r="F88" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B88,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G88" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B88,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5835,16 +7512,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D89" s="12">
+      <c r="D89" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$49,BANDAS!$F$49)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E89" s="13">
+      <c r="E89" s="16">
         <f>D89*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="90">
+      <c r="F89" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B89,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G89" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B89,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5860,16 +7545,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D90" s="12">
+      <c r="D90" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$49,BANDAS!$F$49)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E90" s="13">
+      <c r="E90" s="16">
         <f>D90*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="91">
+      <c r="F90" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B90,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G90" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B90,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5885,16 +7578,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D91" s="12">
+      <c r="D91" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$49,BANDAS!$F$49)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E91" s="13">
+      <c r="E91" s="16">
         <f>D91*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="92">
+      <c r="F91" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B91,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G91" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B91,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5910,16 +7611,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D92" s="12">
+      <c r="D92" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E92" s="13">
+      <c r="E92" s="16">
         <f>D92*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="93">
+      <c r="F92" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B92,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G92" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B92,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5935,16 +7644,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E93" s="13">
+      <c r="E93" s="16">
         <f>D93*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="94">
+      <c r="F93" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B93,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G93" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B93,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5960,16 +7677,24 @@
           <t>15 mg</t>
         </is>
       </c>
-      <c r="D94" s="12">
+      <c r="D94" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*15/1,0)*1</f>
         <v/>
       </c>
-      <c r="E94" s="13">
+      <c r="E94" s="16">
         <f>D94*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="95">
+      <c r="F94" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B94,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G94" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B94,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="26" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -5985,16 +7710,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D95" s="12">
+      <c r="D95" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="16">
         <f>D95*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="96">
+      <c r="F95" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B95,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G95" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B95,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -6010,16 +7743,24 @@
           <t>30 mg</t>
         </is>
       </c>
-      <c r="D96" s="12">
+      <c r="D96" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*30/1,0)*1</f>
         <v/>
       </c>
-      <c r="E96" s="13">
+      <c r="E96" s="16">
         <f>D96*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="97">
+      <c r="F96" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B96,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G96" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B96,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="26" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -6035,16 +7776,24 @@
           <t>40 mg</t>
         </is>
       </c>
-      <c r="D97" s="12">
+      <c r="D97" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*40/1,0)*1</f>
         <v/>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="16">
         <f>D97*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="98">
+      <c r="F97" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B97,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G97" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B97,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="26" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -6060,16 +7809,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D98" s="12">
+      <c r="D98" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E98" s="13">
+      <c r="E98" s="16">
         <f>D98*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="99">
+      <c r="F98" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B98,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G98" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B98,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="26" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
           <t>FITNESS</t>
@@ -6085,16 +7842,24 @@
           <t>60 mg</t>
         </is>
       </c>
-      <c r="D99" s="12">
+      <c r="D99" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$50,BANDAS!$F$50)*60/1,0)*1</f>
         <v/>
       </c>
-      <c r="E99" s="13">
+      <c r="E99" s="16">
         <f>D99*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="100">
+      <c r="F99" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B99,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G99" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B99,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="26" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6110,16 +7875,24 @@
           <t>20 mg</t>
         </is>
       </c>
-      <c r="D100" s="12">
+      <c r="D100" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$51,BANDAS!$F$51)*20/1,0)*1</f>
         <v/>
       </c>
-      <c r="E100" s="13">
+      <c r="E100" s="16">
         <f>D100*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="101">
+      <c r="F100" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B100,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G100" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B100,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="26" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6135,16 +7908,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D101" s="12">
+      <c r="D101" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$52,BANDAS!$F$52)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E101" s="13">
+      <c r="E101" s="16">
         <f>D101*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="102">
+      <c r="F101" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B101,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G101" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B101,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="26" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6160,16 +7941,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D102" s="12">
+      <c r="D102" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$52,BANDAS!$F$52)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E102" s="13">
+      <c r="E102" s="16">
         <f>D102*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="103">
+      <c r="F102" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B102,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G102" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B102,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="26" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6185,16 +7974,24 @@
           <t>12 mg</t>
         </is>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$52,BANDAS!$F$52)*12/1,0)*1</f>
         <v/>
       </c>
-      <c r="E103" s="13">
+      <c r="E103" s="16">
         <f>D103*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="104">
+      <c r="F103" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B103,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G103" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B103,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="26" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6210,16 +8007,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D104" s="12">
+      <c r="D104" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$53,BANDAS!$F$53)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E104" s="13">
+      <c r="E104" s="16">
         <f>D104*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="105">
+      <c r="F104" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B104,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G104" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B104,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="26" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6235,16 +8040,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D105" s="12">
+      <c r="D105" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$53,BANDAS!$F$53)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E105" s="13">
+      <c r="E105" s="16">
         <f>D105*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="106">
+      <c r="F105" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B105,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G105" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B105,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="26" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6260,16 +8073,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D106" s="12">
+      <c r="D106" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$54,BANDAS!$F$54)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E106" s="13">
+      <c r="E106" s="16">
         <f>D106*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="107">
+      <c r="F106" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B106,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G106" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B106,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="26" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6285,16 +8106,24 @@
           <t>50 mg</t>
         </is>
       </c>
-      <c r="D107" s="12">
+      <c r="D107" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$54,BANDAS!$F$54)*50/1,0)*1</f>
         <v/>
       </c>
-      <c r="E107" s="13">
+      <c r="E107" s="16">
         <f>D107*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="108">
+      <c r="F107" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B107,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G107" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B107,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="26" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6310,16 +8139,24 @@
           <t>2 mg</t>
         </is>
       </c>
-      <c r="D108" s="12">
+      <c r="D108" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$55,BANDAS!$F$55)*2/1,0)*1</f>
         <v/>
       </c>
-      <c r="E108" s="13">
+      <c r="E108" s="16">
         <f>D108*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="109">
+      <c r="F108" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B108,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G108" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B108,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="26" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6335,16 +8172,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D109" s="12">
+      <c r="D109" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$56,BANDAS!$F$56)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E109" s="13">
+      <c r="E109" s="16">
         <f>D109*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="110">
+      <c r="F109" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B109,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G109" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B109,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="26" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6360,16 +8205,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D110" s="12">
+      <c r="D110" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$56,BANDAS!$F$56)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E110" s="13">
+      <c r="E110" s="16">
         <f>D110*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="111">
+      <c r="F110" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B110,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G110" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B110,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="26" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6385,16 +8238,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D111" s="12">
+      <c r="D111" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$57,BANDAS!$F$57)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E111" s="13">
+      <c r="E111" s="16">
         <f>D111*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="112">
+      <c r="F111" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B111,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G111" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B111,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="26" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6410,16 +8271,24 @@
           <t>100 mg</t>
         </is>
       </c>
-      <c r="D112" s="12">
+      <c r="D112" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$58,BANDAS!$F$58)*100/1,0)*1</f>
         <v/>
       </c>
-      <c r="E112" s="13">
+      <c r="E112" s="16">
         <f>D112*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="113">
+      <c r="F112" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B112,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G112" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B112,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="26" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6435,16 +8304,24 @@
           <t>500 mg</t>
         </is>
       </c>
-      <c r="D113" s="12">
+      <c r="D113" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$58,BANDAS!$F$58)*500/1,0)*1</f>
         <v/>
       </c>
-      <c r="E113" s="13">
+      <c r="E113" s="16">
         <f>D113*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="114">
+      <c r="F113" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B113,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G113" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B113,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6460,16 +8337,24 @@
           <t>1000 mg</t>
         </is>
       </c>
-      <c r="D114" s="12">
+      <c r="D114" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$58,BANDAS!$F$58)*1000/1,0)*1</f>
         <v/>
       </c>
-      <c r="E114" s="13">
+      <c r="E114" s="16">
         <f>D114*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="115">
+      <c r="F114" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B114,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G114" s="14">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B114,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="26" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6485,16 +8370,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D115" s="12">
+      <c r="D115" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$59,BANDAS!$F$59)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E115" s="13">
+      <c r="E115" s="16">
         <f>D115*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="116">
+      <c r="F115" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B115,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G115" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B115,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="26" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6510,16 +8403,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D116" s="12">
+      <c r="D116" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$60,BANDAS!$F$60)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E116" s="13">
+      <c r="E116" s="16">
         <f>D116*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="117">
+      <c r="F116" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B116,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G116" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B116,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="26" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6535,16 +8436,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D117" s="12">
+      <c r="D117" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$60,BANDAS!$F$60)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E117" s="13">
+      <c r="E117" s="16">
         <f>D117*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="118">
+      <c r="F117" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B117,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G117" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B117,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="26" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6560,16 +8469,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D118" s="12">
+      <c r="D118" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$61,BANDAS!$F$61)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E118" s="13">
+      <c r="E118" s="16">
         <f>D118*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="119">
+      <c r="F118" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B118,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G118" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B118,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="26" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6585,16 +8502,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D119" s="12">
+      <c r="D119" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$61,BANDAS!$F$61)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E119" s="13">
+      <c r="E119" s="16">
         <f>D119*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="120">
+      <c r="F119" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B119,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G119" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B119,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="26" customHeight="1">
       <c r="A120" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6610,16 +8535,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D120" s="12">
+      <c r="D120" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$62,BANDAS!$F$62)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E120" s="13">
+      <c r="E120" s="16">
         <f>D120*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="121">
+      <c r="F120" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B120,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G120" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B120,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="26" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6635,16 +8568,24 @@
           <t>5 mg</t>
         </is>
       </c>
-      <c r="D121" s="12">
+      <c r="D121" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$63,BANDAS!$F$63)*5/1,0)*1</f>
         <v/>
       </c>
-      <c r="E121" s="13">
+      <c r="E121" s="16">
         <f>D121*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="122">
+      <c r="F121" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B121,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G121" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B121,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="26" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6660,16 +8601,24 @@
           <t>10 mg</t>
         </is>
       </c>
-      <c r="D122" s="12">
+      <c r="D122" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$63,BANDAS!$F$63)*10/1,0)*1</f>
         <v/>
       </c>
-      <c r="E122" s="13">
+      <c r="E122" s="16">
         <f>D122*BANDAS!$E$5</f>
         <v/>
       </c>
-    </row>
-    <row r="123">
+      <c r="F122" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B122,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G122" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B122,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
@@ -6685,17 +8634,25 @@
           <t>1 mg</t>
         </is>
       </c>
-      <c r="D123" s="12">
+      <c r="D123" s="15">
         <f>ROUND(AVERAGE(BANDAS!$E$64,BANDAS!$F$64)*1/1,0)*1</f>
         <v/>
       </c>
-      <c r="E123" s="13">
+      <c r="E123" s="16">
         <f>D123*BANDAS!$E$5</f>
         <v/>
       </c>
+      <c r="F123" s="12">
+        <f>INDEX(BANDAS!$H$9:$H$64,MATCH($B123,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
+      <c r="G123" s="13">
+        <f>INDEX(BANDAS!$G$9:$G$64,MATCH($B123,BANDAS!$B$9:$B$64,0))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:E123"/>
+  <autoFilter ref="A5:G123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6733,28 +8690,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>MÉXICO (MXN)</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>USA (USD)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>DE DÓNDE SALE EL PRECIO</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="16" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="19" t="n"/>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
@@ -6778,16 +8735,16 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>LAS CIFRAS</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="8" t="inlineStr">
@@ -6795,15 +8752,15 @@
           <t>Valor del catálogo a precio al consumidor</t>
         </is>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="20">
         <f>SUM('MÉXICO'!$D$6:$D$123)</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="21">
         <f>SUM('USA'!$D$6:$D$123)</f>
         <v/>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>Una unidad de cada presentación. No es una previsión de ventas.</t>
         </is>
@@ -6815,15 +8772,15 @@
           <t>Presentaciones</t>
         </is>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="23">
         <f>COUNTA('MÉXICO'!$B$6:$B$123)</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="23">
         <f>COUNTA('USA'!$B$6:$B$123)</f>
         <v/>
       </c>
-      <c r="G12" s="19" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="inlineStr">
@@ -6831,31 +8788,31 @@
           <t>Precio medio por presentación</t>
         </is>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="20">
         <f>IF(C12=0,"",C11/C12)</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="21">
         <f>IF(D12=0,"",D11/D12)</f>
         <v/>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>México sale más caro que USA por la prima del retail mexicano, que está en BANDAS.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>CUÁNTO CREERSE CADA PRECIO</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
@@ -6863,15 +8820,15 @@
           <t>Compuestos con cifra publicada para ese compuesto</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="23">
         <f>COUNTIF(BANDAS!$G$9:$G$64,"V")</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="23">
         <f>COUNTIF(BANDAS!$G$9:$G$64,"V")</f>
         <v/>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>Marcados V en BANDAS. Hay un precio real localizado para esa molécula.</t>
         </is>
@@ -6883,15 +8840,15 @@
           <t>Compuestos por banda de su clase</t>
         </is>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="23">
         <f>COUNTIF(BANDAS!$G$9:$G$64,"D")</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="23">
         <f>COUNTIF(BANDAS!$G$9:$G$64,"D")</f>
         <v/>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>Marcados D. No hay cifra para esa molécula; se usa la de su clase, que sí está comprobada.</t>
         </is>
@@ -6903,13 +8860,13 @@
           <t>Fuentes consultadas</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>Listadas en FUENTES, con el dato que dio cada una.</t>
         </is>
@@ -6921,27 +8878,27 @@
           <t>Precios reales de competidores mexicanos</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="20" t="inlineStr"/>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr"/>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>Ocho compuestos con precio publicado por una tienda mexicana, con nombre. En BANDAS.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>LO QUE ESTE ESTUDIO NO CONTESTA</t>
         </is>
       </c>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
@@ -7007,17 +8964,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H64"/>
+  <dimension ref="A2:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="82" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="74" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -7035,12 +8993,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Tipo de cambio USD → MXN</t>
         </is>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="25" t="n">
         <v>17.5</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -7050,12 +9008,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Prima del retail mexicano sobre el estadounidense</t>
         </is>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="25" t="n">
         <v>1.35</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -7102,2139 +9060,2482 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>DE DÓNDE SALE</t>
+          <t>EN QUÉ SE BASA</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>ENLACE</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>AHK-Cu</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="27" t="n">
         <v>0.7</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="27" t="n">
         <v>1.3</v>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>AHK-Cu: 50 mg $35–65, sigue a GHK-Cu con prima</t>
         </is>
       </c>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>CU</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>GHK-Cu</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="27" t="n">
         <v>0.8</v>
       </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>peptide.promo · GHK-Cu desde $0.50/mg; 50 mg $20–40</t>
         </is>
       </c>
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>GLOW Blend</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="27" t="n">
         <v>1.7</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="27" t="n">
         <v>3.1</v>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>Mezcla GLOW 70 mg: $120–220 el vial</t>
         </is>
       </c>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Glutathione</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="27" t="n">
         <v>0.05</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="27" t="n">
         <v>0.1</v>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>Glutatión: 600 mg $30–60, es materia prima</t>
         </is>
       </c>
+      <c r="I12" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>KL</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>KLOW Blend</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="27" t="n">
         <v>1.9</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="27" t="n">
         <v>3.25</v>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>Mezcla KLOW 80 mg: $150–260 el vial</t>
         </is>
       </c>
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>KPV</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="27" t="n">
         <v>5.5</v>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>KPV: 10 mg $30–55</t>
         </is>
       </c>
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Matrixyl</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>Matrixyl: 10 mg $50–90</t>
         </is>
       </c>
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>MT1</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Melanotan I</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="27" t="n">
         <v>5.5</v>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>Melanotán 1: sigue a melanotán 2 con menos demanda</t>
         </is>
       </c>
+      <c r="I16" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>MT2</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Melanotan II</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="27" t="n">
         <v>2.2</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="27" t="n">
         <v>6.4</v>
       </c>
-      <c r="G17" s="27" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>nationwidepeptides · melanotán 2 $22–30 y $47–64 según presentación</t>
         </is>
       </c>
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>https://www.nationwidepeptides.com/products/melanotan-2/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Oxytocin</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="H18" s="28" t="inlineStr">
         <is>
           <t>Oxitocina: 5 mg $25–45</t>
         </is>
       </c>
+      <c r="I18" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>PT-141</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G19" s="27" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H19" s="26" t="inlineStr">
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>biotechpeptides / nexaph · PT-141 10 mg; nexaph $160 es el techo del mercado</t>
         </is>
       </c>
+      <c r="I19" s="29" t="inlineStr">
+        <is>
+          <t>https://biotechpeptides.com/product/bpc-157/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>NP8</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Snap-8</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>BEAUTY</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="27" t="n">
         <v>5.5</v>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H20" s="26" t="inlineStr">
+      <c r="H20" s="28" t="inlineStr">
         <is>
           <t>Snap-8: 10 mg $30–55</t>
         </is>
       </c>
+      <c r="I20" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>5-Amino-1MQ</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="F21" s="27" t="n">
         <v>2.2</v>
       </c>
-      <c r="G21" s="25" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H21" s="26" t="inlineStr">
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>5-Amino-1MQ: 50 mg $60–110</t>
         </is>
       </c>
+      <c r="I21" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>AICAR</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E22" s="24" t="n">
+      <c r="E22" s="27" t="n">
         <v>0.8</v>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="27" t="n">
         <v>1.4</v>
       </c>
-      <c r="G22" s="25" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H22" s="26" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>AICAR: 50 mg $40–70</t>
         </is>
       </c>
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>AOD-9604</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G23" s="25" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>Fragmentos lipolíticos: AOD-9604 5 mg $25–45</t>
         </is>
       </c>
+      <c r="I23" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>AX</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Adamax</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E24" s="24" t="n">
+      <c r="E24" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="G24" s="25" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H24" s="26" t="inlineStr">
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>Adamax: 10 mg $60–110, oferta escasa</t>
         </is>
       </c>
+      <c r="I24" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>APT</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Adipotide</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H25" s="26" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>Adipotide: oferta escasa, prima sobre AOD</t>
         </is>
       </c>
+      <c r="I25" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Ara-290</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E26" s="24" t="n">
+      <c r="E26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="24" t="n">
+      <c r="F26" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="G26" s="25" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H26" s="26" t="inlineStr">
+      <c r="H26" s="28" t="inlineStr">
         <is>
           <t>Ara-290: 10 mg $60–110, oferta escasa</t>
         </is>
       </c>
+      <c r="I26" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>BPC-157</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="E27" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="F27" s="24" t="n">
+      <c r="F27" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="G27" s="27" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H27" s="26" t="inlineStr">
+      <c r="H27" s="28" t="inlineStr">
         <is>
           <t>peptide.promo · BPC-157 desde $2.46/mg; vial 5 mg $20–35 en peptidesexplorer</t>
         </is>
       </c>
+      <c r="I27" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>BPC-157 + TB-500</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E28" s="24" t="n">
+      <c r="E28" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="F28" s="24" t="n">
+      <c r="F28" s="27" t="n">
         <v>7.5</v>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H28" s="26" t="inlineStr">
+      <c r="H28" s="28" t="inlineStr">
         <is>
           <t>Mezcla BPC-157 + TB-500: media de las bandas de sus dos componentes</t>
         </is>
       </c>
+      <c r="I28" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>CJC-1295 (DAC)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="G29" s="25" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H29" s="26" t="inlineStr">
+      <c r="H29" s="28" t="inlineStr">
         <is>
           <t>CJC-1295 con DAC: prima sobre el sin DAC por vida media</t>
         </is>
       </c>
+      <c r="I29" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>CJC-1295 (no DAC)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E30" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G30" s="25" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H30" s="26" t="inlineStr">
+      <c r="H30" s="28" t="inlineStr">
         <is>
           <t>Clase secretagogos GH</t>
         </is>
       </c>
+      <c r="I30" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>CP</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>CJC-1295 + Ipamorelin</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G31" s="27" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H31" s="26" t="inlineStr">
+      <c r="H31" s="28" t="inlineStr">
         <is>
           <t>accelerate-labs · CJC-1295 5 mg + Ipamorelina 5 mg $91.99</t>
         </is>
       </c>
+      <c r="I31" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Cagri + Sema</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E32" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="G32" s="25" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H32" s="26" t="inlineStr">
+      <c r="H32" s="28" t="inlineStr">
         <is>
           <t>Clase GLP-1 combinada (cagri + sema)</t>
         </is>
       </c>
+      <c r="I32" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>CGL</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Cagrilintide</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E33" s="24" t="n">
+      <c r="E33" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="G33" s="25" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H33" s="26" t="inlineStr">
+      <c r="H33" s="28" t="inlineStr">
         <is>
           <t>Clase GLP-1/amilina (cagrilintida)</t>
         </is>
       </c>
+      <c r="I33" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>GHRP-2</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E34" s="24" t="n">
+      <c r="E34" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G34" s="25" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H34" s="26" t="inlineStr">
+      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>Clase secretagogos GH</t>
         </is>
       </c>
+      <c r="I34" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>GHRP-6</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E35" s="24" t="n">
+      <c r="E35" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="24" t="n">
+      <c r="F35" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G35" s="25" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H35" s="26" t="inlineStr">
+      <c r="H35" s="28" t="inlineStr">
         <is>
           <t>Clase secretagogos GH</t>
         </is>
       </c>
+      <c r="I35" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>HGH 191AA</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>iu</t>
         </is>
       </c>
-      <c r="E36" s="24" t="n">
+      <c r="E36" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="F36" s="24" t="n">
+      <c r="F36" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="G36" s="25" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H36" s="26" t="inlineStr">
+      <c r="H36" s="28" t="inlineStr">
         <is>
           <t>HGH 191AA por UI: 10 iu $25–45</t>
         </is>
       </c>
+      <c r="I36" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>HX</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Hexarelin</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E37" s="24" t="n">
+      <c r="E37" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="G37" s="25" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H37" s="26" t="inlineStr">
+      <c r="H37" s="28" t="inlineStr">
         <is>
           <t>Clase secretagogos GH, prima por potencia y menor oferta</t>
         </is>
       </c>
+      <c r="I37" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>IG</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>IGF-1 LR3</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E38" s="24" t="n">
+      <c r="E38" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="F38" s="24" t="n">
+      <c r="F38" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="G38" s="25" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H38" s="26" t="inlineStr">
+      <c r="H38" s="28" t="inlineStr">
         <is>
           <t>IGF-1 LR3: vial de 1 mg $40–80, mercado estrecho</t>
         </is>
       </c>
+      <c r="I38" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>IPA</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Ipamorelin</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E39" s="24" t="n">
+      <c r="E39" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="24" t="n">
+      <c r="F39" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G39" s="25" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H39" s="26" t="inlineStr">
+      <c r="H39" s="28" t="inlineStr">
         <is>
           <t>Clase secretagogos GH: vial 5 mg $20–45 (peptidepros, directpeptides)</t>
         </is>
       </c>
+      <c r="I39" s="29" t="inlineStr">
+        <is>
+          <t>https://www.peptidepros.net/</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>LC</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>L-Carnitine</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E40" s="24" t="n">
+      <c r="E40" s="27" t="n">
         <v>0.04</v>
       </c>
-      <c r="F40" s="24" t="n">
+      <c r="F40" s="27" t="n">
         <v>0.075</v>
       </c>
-      <c r="G40" s="25" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H40" s="26" t="inlineStr">
+      <c r="H40" s="28" t="inlineStr">
         <is>
           <t>L-Carnitina: 600 mg $25–45, es materia prima</t>
         </is>
       </c>
+      <c r="I40" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>MIC</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Lipo-C + B12</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="E41" s="24" t="n">
+      <c r="E41" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F41" s="24" t="n">
+      <c r="F41" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="G41" s="25" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H41" s="26" t="inlineStr">
+      <c r="H41" s="28" t="inlineStr">
         <is>
           <t>Lipo-C + B12 por ml: vial de 10 ml $60–120</t>
         </is>
       </c>
+      <c r="I41" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>MOTS-c</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E42" s="24" t="n">
+      <c r="E42" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="24" t="n">
+      <c r="F42" s="27" t="n">
         <v>5.5</v>
       </c>
-      <c r="G42" s="25" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H42" s="26" t="inlineStr">
+      <c r="H42" s="28" t="inlineStr">
         <is>
           <t>MOTS-c: 10 mg $30–55</t>
         </is>
       </c>
+      <c r="I42" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>Mazdutide</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E43" s="24" t="n">
+      <c r="E43" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="24" t="n">
+      <c r="F43" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="G43" s="25" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H43" s="26" t="inlineStr">
+      <c r="H43" s="28" t="inlineStr">
         <is>
           <t>Clase GLP-1 nueva (mazdutida): menos oferta que semaglutida</t>
         </is>
       </c>
+      <c r="I43" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="inlineStr">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Retatrutide</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E44" s="24" t="n">
+      <c r="E44" s="27" t="n">
         <v>4.8</v>
       </c>
-      <c r="F44" s="24" t="n">
+      <c r="F44" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="G44" s="27" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H44" s="26" t="inlineStr">
+      <c r="H44" s="28" t="inlineStr">
         <is>
           <t>peptilabresearch · retatrutida 10 mg $56.40; vial 5 mg $24–50</t>
         </is>
       </c>
+      <c r="I44" s="29" t="inlineStr">
+        <is>
+          <t>https://peptilabresearch.com/shop/</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>2S</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>SS-31</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E45" s="24" t="n">
+      <c r="E45" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F45" s="24" t="n">
+      <c r="F45" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="G45" s="25" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H45" s="26" t="inlineStr">
+      <c r="H45" s="28" t="inlineStr">
         <is>
           <t>SS-31: 10 mg $40–70</t>
         </is>
       </c>
+      <c r="I45" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>SM</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>Semaglutide</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E46" s="24" t="n">
+      <c r="E46" s="27" t="n">
         <v>2.75</v>
       </c>
-      <c r="F46" s="24" t="n">
+      <c r="F46" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G46" s="27" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H46" s="26" t="inlineStr">
+      <c r="H46" s="28" t="inlineStr">
         <is>
           <t>peptide.promo · semaglutida desde $2.75/mg; vial 5 mg $20–40</t>
         </is>
       </c>
+      <c r="I46" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>SMO</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>Sermorelin</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E47" s="24" t="n">
+      <c r="E47" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="24" t="n">
+      <c r="F47" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G47" s="25" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H47" s="26" t="inlineStr">
+      <c r="H47" s="28" t="inlineStr">
         <is>
           <t>Clase secretagogos GH</t>
         </is>
       </c>
+      <c r="I47" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="23" t="inlineStr">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="B48" s="23" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>TB-500</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E48" s="24" t="n">
+      <c r="E48" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="24" t="n">
+      <c r="F48" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G48" s="27" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H48" s="26" t="inlineStr">
+      <c r="H48" s="28" t="inlineStr">
         <is>
           <t>peptilabresearch · TB-500 10 mg $29.99 (lista $49.99)</t>
         </is>
       </c>
+      <c r="I48" s="29" t="inlineStr">
+        <is>
+          <t>https://peptilabresearch.com/shop/</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>TSM</t>
         </is>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Tesamorelin</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E49" s="24" t="n">
+      <c r="E49" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="24" t="n">
+      <c r="F49" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G49" s="25" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H49" s="26" t="inlineStr">
+      <c r="H49" s="28" t="inlineStr">
         <is>
           <t>Clase secretagogos GH</t>
         </is>
       </c>
+      <c r="I49" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="26" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Tirzepatide</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>FITNESS</t>
-        </is>
-      </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>FITNESS</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E50" s="24" t="n">
+      <c r="E50" s="27" t="n">
         <v>3.09</v>
       </c>
-      <c r="F50" s="24" t="n">
+      <c r="F50" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G50" s="27" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H50" s="26" t="inlineStr">
+      <c r="H50" s="28" t="inlineStr">
         <is>
           <t>peptide.promo · tirzepatida desde $3.09/mg; vial 5 mg $20–45</t>
         </is>
       </c>
+      <c r="I50" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>CTL</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>Cartalax</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E51" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="F51" s="24" t="n">
+      <c r="F51" s="27" t="n">
         <v>6.5</v>
       </c>
-      <c r="G51" s="25" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H51" s="26" t="inlineStr">
+      <c r="H51" s="28" t="inlineStr">
         <is>
           <t>Bioreguladores (cartalax): 20 mg $70–130</t>
         </is>
       </c>
+      <c r="I51" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="A52" s="26" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>DSIP</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E52" s="24" t="n">
+      <c r="E52" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F52" s="24" t="n">
+      <c r="F52" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="G52" s="25" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H52" s="26" t="inlineStr">
+      <c r="H52" s="28" t="inlineStr">
         <is>
           <t>DSIP: 5 mg $20–35</t>
         </is>
       </c>
+      <c r="I52" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>DX</t>
         </is>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>Dihexa</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E53" s="24" t="n">
+      <c r="E53" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F53" s="24" t="n">
+      <c r="F53" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="G53" s="25" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H53" s="26" t="inlineStr">
+      <c r="H53" s="28" t="inlineStr">
         <is>
           <t>Dihexa: 5 mg $40–75</t>
         </is>
       </c>
+      <c r="I53" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="23" t="inlineStr">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>Epithalon</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C54" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E54" s="24" t="n">
+      <c r="E54" s="27" t="n">
         <v>1.38</v>
       </c>
-      <c r="F54" s="24" t="n">
+      <c r="F54" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G54" s="27" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H54" s="26" t="inlineStr">
+      <c r="H54" s="28" t="inlineStr">
         <is>
           <t>peptilabresearch · epitalón 10 mg $13.79 (lista $22.99)</t>
         </is>
       </c>
+      <c r="I54" s="29" t="inlineStr">
+        <is>
+          <t>https://peptilabresearch.com/shop/</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>FOXO4-DRI</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E55" s="24" t="n">
+      <c r="E55" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="F55" s="24" t="n">
+      <c r="F55" s="27" t="n">
         <v>75</v>
       </c>
-      <c r="G55" s="25" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H55" s="26" t="inlineStr">
+      <c r="H55" s="28" t="inlineStr">
         <is>
           <t>FOXO4-DRI: 2 mg $80–150, el más caro del catálogo</t>
         </is>
       </c>
+      <c r="I55" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+      <c r="A56" s="26" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>KissPeptin-10</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E56" s="24" t="n">
+      <c r="E56" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F56" s="24" t="n">
+      <c r="F56" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="G56" s="25" t="inlineStr">
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H56" s="26" t="inlineStr">
+      <c r="H56" s="28" t="inlineStr">
         <is>
           <t>Kisspeptina-10: 5 mg $25–50</t>
         </is>
       </c>
+      <c r="I56" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="23" t="inlineStr">
+      <c r="A57" s="26" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>Melatonin</t>
         </is>
       </c>
-      <c r="C57" s="23" t="inlineStr">
+      <c r="C57" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D57" s="23" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E57" s="24" t="n">
+      <c r="E57" s="27" t="n">
         <v>1.5</v>
       </c>
-      <c r="F57" s="24" t="n">
+      <c r="F57" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G57" s="25" t="inlineStr">
+      <c r="G57" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H57" s="26" t="inlineStr">
+      <c r="H57" s="28" t="inlineStr">
         <is>
           <t>Melatonina: 10 mg $15–30</t>
         </is>
       </c>
+      <c r="I57" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="23" t="inlineStr">
+      <c r="A58" s="26" t="inlineStr">
         <is>
           <t>NJ</t>
         </is>
       </c>
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>NAD+</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
+      <c r="C58" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D58" s="23" t="inlineStr">
+      <c r="D58" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E58" s="24" t="n">
+      <c r="E58" s="27" t="n">
         <v>0.14</v>
       </c>
-      <c r="F58" s="24" t="n">
+      <c r="F58" s="27" t="n">
         <v>0.3</v>
       </c>
-      <c r="G58" s="27" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="H58" s="26" t="inlineStr">
+      <c r="H58" s="28" t="inlineStr">
         <is>
           <t>peptide.promo · NAD+ ≈ $0.14/mg</t>
         </is>
       </c>
+      <c r="I58" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="23" t="inlineStr">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="B59" s="23" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>Pinealon</t>
         </is>
       </c>
-      <c r="C59" s="23" t="inlineStr">
+      <c r="C59" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D59" s="23" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E59" s="24" t="n">
+      <c r="E59" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="F59" s="24" t="n">
+      <c r="F59" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G59" s="25" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H59" s="26" t="inlineStr">
+      <c r="H59" s="28" t="inlineStr">
         <is>
           <t>Bioreguladores (pinealón): 10 mg $50–90</t>
         </is>
       </c>
+      <c r="I59" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>Selank</t>
         </is>
       </c>
-      <c r="C60" s="23" t="inlineStr">
+      <c r="C60" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D60" s="23" t="inlineStr">
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E60" s="24" t="n">
+      <c r="E60" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F60" s="24" t="n">
+      <c r="F60" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G60" s="25" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H60" s="26" t="inlineStr">
+      <c r="H60" s="28" t="inlineStr">
         <is>
           <t>Nootrópicos peptídicos (selank): 5 mg $20–40</t>
         </is>
       </c>
+      <c r="I60" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="23" t="inlineStr">
+      <c r="A61" s="26" t="inlineStr">
         <is>
           <t>SX</t>
         </is>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>Semax</t>
         </is>
       </c>
-      <c r="C61" s="23" t="inlineStr">
+      <c r="C61" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D61" s="23" t="inlineStr">
+      <c r="D61" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E61" s="24" t="n">
+      <c r="E61" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F61" s="24" t="n">
+      <c r="F61" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G61" s="25" t="inlineStr">
+      <c r="G61" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H61" s="26" t="inlineStr">
+      <c r="H61" s="28" t="inlineStr">
         <is>
           <t>Nootrópicos peptídicos (semax): 5 mg $20–40</t>
         </is>
       </c>
+      <c r="I61" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="23" t="inlineStr">
+      <c r="A62" s="26" t="inlineStr">
         <is>
           <t>TY</t>
         </is>
       </c>
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>Thymalin</t>
         </is>
       </c>
-      <c r="C62" s="23" t="inlineStr">
+      <c r="C62" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D62" s="23" t="inlineStr">
+      <c r="D62" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E62" s="24" t="n">
+      <c r="E62" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="F62" s="24" t="n">
+      <c r="F62" s="27" t="n">
         <v>8.5</v>
       </c>
-      <c r="G62" s="25" t="inlineStr">
+      <c r="G62" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H62" s="26" t="inlineStr">
+      <c r="H62" s="28" t="inlineStr">
         <is>
           <t>Timalina: 10 mg $45–85</t>
         </is>
       </c>
+      <c r="I62" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="23" t="inlineStr">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>Ta1</t>
         </is>
       </c>
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>Thymosin Alpha-1</t>
         </is>
       </c>
-      <c r="C63" s="23" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D63" s="23" t="inlineStr">
+      <c r="D63" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E63" s="24" t="n">
+      <c r="E63" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F63" s="24" t="n">
+      <c r="F63" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="G63" s="25" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H63" s="26" t="inlineStr">
+      <c r="H63" s="28" t="inlineStr">
         <is>
           <t>Timosina alfa-1: 5 mg $35–65</t>
         </is>
       </c>
+      <c r="I63" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="26" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>Vitamin B12</t>
         </is>
       </c>
-      <c r="C64" s="23" t="inlineStr">
+      <c r="C64" s="26" t="inlineStr">
         <is>
           <t>LONGEVITY</t>
         </is>
       </c>
-      <c r="D64" s="23" t="inlineStr">
+      <c r="D64" s="26" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="E64" s="24" t="n">
+      <c r="E64" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="F64" s="24" t="n">
+      <c r="F64" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="G64" s="25" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H64" s="26" t="inlineStr">
+      <c r="H64" s="28" t="inlineStr">
         <is>
           <t>Vitamina B12 por vial de 1 mg/ml: $15–30</t>
         </is>
       </c>
+      <c r="I64" s="29" t="inlineStr">
+        <is>
+          <t>https://peptide.promo/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9291,469 +11592,469 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>peptide.promo</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Comparador $/mg. Semaglutida $2.75/mg · tirzepatida $3.09/mg · BPC-157 $2.46/mg · GHK-Cu $0.50/mg · NAD+ $0.14/mg</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>https://peptide.promo/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>PeptidesExplorer</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>Rangos por vial: semaglutida 5 mg $20–40 · tirzepatida 5 mg $20–45 · retatrutida 5 mg $24–50 · BPC-157 5 mg $20–35 · GHK-Cu 50 mg $20–40</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>https://peptidesexplorer.com/blog/how-much-do-peptides-cost</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>PeptiLab Research</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>BPC-157 10 mg $22.79 · TB-500 10 mg $29.99 · epitalón 10 mg $13.79 · retatrutida 10 mg $56.40 (con descuento)</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>https://peptilabresearch.com/shop/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>peptideprices.net</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Comparador $/10 mg sobre 51 vendedores, con COA y fecha de comprobación por listado</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>https://peptideprices.net/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>PepsTracker</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>Comparador sobre 24 vendedores; volatilidad semanal de tirzepatida y retatrutida</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>https://pepstracker.com/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>The Peptide Catalog</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Índice de precios trimestral, tendencia a 90 días</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>https://thepeptidecatalog.com/articles/peptide-pricing-report-q1-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>PeptideDeck</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>BPC-157 $49–100 por vial en 2026; $5–8/mg de vendedor legítimo; por debajo de $3/mg es señal de alarma</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>https://www.peptidedeck.com/blog/bpc-157-for-sale</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Biotech Peptides</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Precio de lista de BPC-157 5 mg y mezcla CJC-1295 + Ipamorelina 10 mg</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>https://biotechpeptides.com/product/bpc-157/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Nationwide Peptides</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>Melanotán 2: $22–30 y $47–64 según presentación</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>https://www.nationwidepeptides.com/products/melanotan-2/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>NEXAPH</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>PT-141 $160 — techo del mercado, útil como referencia superior</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>https://nexaph.com/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Peptide Pros</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>Catálogo de secretagogos GH: GHRP-2 5 mg, GHRP-6 5 mg, hexarelina 2 mg, ipamorelina 2 mg, sermorelina 2 mg, tesamorelina 5 mg</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>https://www.peptidepros.net/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Direct Peptides</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>Catálogo de secretagogos y de la línea estética (GHK-Cu, KPV, melanotán 2, oxitocina, PT-141)</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>https://directpeptides.com/products</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Limitless Labs</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>Kits: semaglutida desde $153.13 (5–30 mg) · tirzepatida desde $175 (5–60 mg) · retatrutida desde $218.75 (5–60 mg)</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>https://www.limitlesslabs.us/us</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>EXOMA Peptides</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>Epitalón $700 · GHK-Cu $520 · BPC-157 desde $610 · BPC-157+TB-500 $1,399 · GLOW $2,090 · BPC+TB+KPV $2,999 MXN</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>https://exomapeptides.mx/comprar-peptidos-mexico</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>ZELARA</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>BPC-157 5 mg $673 MXN · TB-500 5 mg $1,449 MXN, ambos con COA por lote</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>https://zelara.com.mx/productos</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>ViuPeptides</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Catálogo MX con precios en pesos: tirzepatida, retatrutida, GHK-Cu, BPC-157, TB-500</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>https://viupeptides.com.mx/comprar-peptidos-mexico/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Singular Biotech</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>Catálogo MX: BPC-157, TB-500, NAD+, GHK-Cu, MOTS-c</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>https://singularbiotech.mx/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>NutricostMx</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>Catálogo MX 99 % pureza, envío gratis desde $2,499 MXN</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>https://nutricost.com.mx/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>peptido.info</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Referencia de mercado MX: USD 30–60 por vial de 5 mg importado, o MXN 500–1,000 por vial</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>https://peptido.info/peptidos-en-mexico-donde-comprarlos-y-cuales-hay-disponibles/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>exomapeptides.mx — retatrutida</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>Retatrutida $960 MXN; otra fuente MX la sitúa desde $1,700</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>https://exomapeptides.mx/producto/retatrutida</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Tipo de cambio</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Investing.com</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>USD/MXN 17.35 al cierre consultado; media 2026 ≈ 17.47. En el libro se usa 17.50</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>https://es.investing.com/currencies/usd-mxn-historical-data</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>NOTA SOBRE EL MÉTODO</t>
         </is>
